--- a/Luban/Excel/宝器.xlsx
+++ b/Luban/Excel/宝器.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9060"/>
+    <workbookView windowWidth="22188" windowHeight="9060"/>
   </bookViews>
   <sheets>
     <sheet name="宝器" sheetId="1" r:id="rId1"/>
@@ -1099,7 +1099,7 @@
     <t>技,6</t>
   </si>
   <si>
-    <t>至多持有2个异常状态</t>
+    <t>战斗中角色至多持有3个异常状态</t>
   </si>
   <si>
     <t>拂容绫+1</t>

--- a/Luban/Excel/宝器.xlsx
+++ b/Luban/Excel/宝器.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDB4A1E9-3936-4D0F-AACA-7C4B9AF8E295}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9060"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="宝器" sheetId="1" r:id="rId1"/>
@@ -1165,14 +1171,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="22">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1194,345 +1194,22 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <sz val="9"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="11">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1568,268 +1245,26 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
@@ -1838,77 +1273,27 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2193,24 +1578,24 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I246"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
     <col min="4" max="4" width="12" style="1" customWidth="1"/>
-    <col min="5" max="6" width="17.6666666666667" style="1" customWidth="1"/>
-    <col min="7" max="8" width="75.7777777777778" style="1" customWidth="1"/>
-    <col min="9" max="9" width="21.1111111111111" style="1" customWidth="1"/>
+    <col min="5" max="6" width="17.625" style="1" customWidth="1"/>
+    <col min="7" max="8" width="75.75" style="1" customWidth="1"/>
+    <col min="9" max="9" width="21.125" style="1" customWidth="1"/>
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.6" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2229,11 +1614,11 @@
       </c>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
-      <c r="I1" s="10" t="s">
+      <c r="I1" s="8" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" ht="15.6" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -2244,17 +1629,16 @@
       <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="7"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="9" t="s">
+      <c r="F2" s="5"/>
+      <c r="G2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="H2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="9"/>
-    </row>
-    <row r="3" ht="15.6" spans="1:9">
+      <c r="I2" s="7"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
@@ -2263,15 +1647,15 @@
         <v>12</v>
       </c>
       <c r="D3" s="2"/>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="10"/>
+      <c r="F3" s="8"/>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
     </row>
-    <row r="4" spans="4:8">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.15">
       <c r="D4" s="1" t="s">
         <v>13</v>
       </c>
@@ -2282,82 +1666,82 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" ht="50" customHeight="1" spans="4:8">
+    <row r="5" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G5" s="11" t="s">
+      <c r="G5" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="H5" s="11" t="s">
+      <c r="H5" s="9" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="6" ht="30" spans="4:7">
+    <row r="6" spans="1:9" ht="33" x14ac:dyDescent="0.15">
       <c r="D6" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G6" s="11" t="s">
+      <c r="G6" s="9" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="7" ht="30" spans="4:7">
+    <row r="7" spans="1:9" ht="33" x14ac:dyDescent="0.15">
       <c r="D7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G7" s="11" t="s">
+      <c r="G7" s="9" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="8" ht="30" spans="4:7">
+    <row r="8" spans="1:9" ht="33" x14ac:dyDescent="0.15">
       <c r="D8" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G8" s="11" t="s">
+      <c r="G8" s="9" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="9" ht="30" spans="4:7">
+    <row r="9" spans="1:9" ht="33" x14ac:dyDescent="0.15">
       <c r="D9" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G9" s="11" t="s">
+      <c r="G9" s="9" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="10" ht="30" spans="4:7">
+    <row r="10" spans="1:9" ht="33" x14ac:dyDescent="0.15">
       <c r="D10" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G10" s="11" t="s">
+      <c r="G10" s="9" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="11" ht="30" spans="4:7">
+    <row r="11" spans="1:9" ht="33" x14ac:dyDescent="0.15">
       <c r="D11" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="G11" s="11" t="s">
+      <c r="G11" s="9" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="12" ht="30" spans="4:7">
+    <row r="12" spans="1:9" ht="33" x14ac:dyDescent="0.15">
       <c r="D12" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G12" s="11" t="s">
+      <c r="G12" s="9" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="13" ht="30" spans="4:7">
+    <row r="13" spans="1:9" ht="33" x14ac:dyDescent="0.15">
       <c r="D13" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G13" s="11" t="s">
+      <c r="G13" s="9" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="14" spans="4:7">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.15">
       <c r="D14" s="1" t="s">
         <v>35</v>
       </c>
@@ -2365,7 +1749,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="15" spans="4:7">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.15">
       <c r="D15" s="1" t="s">
         <v>37</v>
       </c>
@@ -2373,7 +1757,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="4:7">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.15">
       <c r="D16" s="1" t="s">
         <v>39</v>
       </c>
@@ -2381,7 +1765,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="17" spans="4:7">
+    <row r="17" spans="4:8" x14ac:dyDescent="0.15">
       <c r="D17" s="1" t="s">
         <v>41</v>
       </c>
@@ -2389,7 +1773,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="18" spans="4:7">
+    <row r="18" spans="4:8" x14ac:dyDescent="0.15">
       <c r="D18" s="1" t="s">
         <v>43</v>
       </c>
@@ -2397,7 +1781,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="19" spans="4:7">
+    <row r="19" spans="4:8" x14ac:dyDescent="0.15">
       <c r="D19" s="1" t="s">
         <v>45</v>
       </c>
@@ -2405,7 +1789,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="20" spans="4:7">
+    <row r="20" spans="4:8" x14ac:dyDescent="0.15">
       <c r="D20" s="1" t="s">
         <v>47</v>
       </c>
@@ -2413,7 +1797,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="21" spans="4:7">
+    <row r="21" spans="4:8" x14ac:dyDescent="0.15">
       <c r="D21" s="1" t="s">
         <v>49</v>
       </c>
@@ -2421,7 +1805,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="4:7">
+    <row r="22" spans="4:8" x14ac:dyDescent="0.15">
       <c r="D22" s="1" t="s">
         <v>51</v>
       </c>
@@ -2429,7 +1813,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="23" spans="4:8">
+    <row r="23" spans="4:8" x14ac:dyDescent="0.15">
       <c r="D23" s="1" t="s">
         <v>53</v>
       </c>
@@ -2437,27 +1821,27 @@
         <v>54</v>
       </c>
     </row>
-    <row r="24" spans="4:4">
+    <row r="24" spans="4:8" x14ac:dyDescent="0.15">
       <c r="D24" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="25" spans="4:4">
+    <row r="25" spans="4:8" x14ac:dyDescent="0.15">
       <c r="D25" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="26" spans="4:4">
+    <row r="26" spans="4:8" x14ac:dyDescent="0.15">
       <c r="D26" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="27" spans="4:4">
+    <row r="27" spans="4:8" x14ac:dyDescent="0.15">
       <c r="D27" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="28" spans="4:7">
+    <row r="28" spans="4:8" x14ac:dyDescent="0.15">
       <c r="D28" s="1" t="s">
         <v>59</v>
       </c>
@@ -2465,57 +1849,57 @@
         <v>60</v>
       </c>
     </row>
-    <row r="29" spans="7:7">
+    <row r="29" spans="4:8" x14ac:dyDescent="0.15">
       <c r="G29" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="30" spans="7:7">
+    <row r="30" spans="4:8" x14ac:dyDescent="0.15">
       <c r="G30" s="1" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="31" spans="7:7">
+    <row r="31" spans="4:8" x14ac:dyDescent="0.15">
       <c r="G31" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="32" spans="7:7">
+    <row r="32" spans="4:8" x14ac:dyDescent="0.15">
       <c r="G32" s="1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="33" spans="7:7">
+    <row r="33" spans="4:7" x14ac:dyDescent="0.15">
       <c r="G33" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="34" spans="7:7">
+    <row r="34" spans="4:7" x14ac:dyDescent="0.15">
       <c r="G34" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="35" spans="7:7">
+    <row r="35" spans="4:7" x14ac:dyDescent="0.15">
       <c r="G35" s="1" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="36" spans="7:7">
+    <row r="36" spans="4:7" x14ac:dyDescent="0.15">
       <c r="G36" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="37" spans="4:4">
+    <row r="37" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D37" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="38" spans="4:4">
+    <row r="38" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D38" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="39" spans="4:7">
+    <row r="39" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D39" s="1" t="s">
         <v>71</v>
       </c>
@@ -2523,7 +1907,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="40" spans="4:7">
+    <row r="40" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D40" s="1" t="s">
         <v>73</v>
       </c>
@@ -2531,7 +1915,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="41" spans="4:7">
+    <row r="41" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D41" s="1" t="s">
         <v>75</v>
       </c>
@@ -2539,7 +1923,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="42" spans="4:7">
+    <row r="42" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D42" s="1" t="s">
         <v>77</v>
       </c>
@@ -2547,7 +1931,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="43" spans="4:7">
+    <row r="43" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D43" s="1" t="s">
         <v>79</v>
       </c>
@@ -2555,7 +1939,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="44" spans="4:7">
+    <row r="44" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D44" s="1" t="s">
         <v>81</v>
       </c>
@@ -2563,7 +1947,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="45" spans="4:7">
+    <row r="45" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D45" s="1" t="s">
         <v>83</v>
       </c>
@@ -2571,7 +1955,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="46" spans="4:7">
+    <row r="46" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D46" s="1" t="s">
         <v>85</v>
       </c>
@@ -2579,7 +1963,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="47" spans="4:7">
+    <row r="47" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D47" s="1" t="s">
         <v>87</v>
       </c>
@@ -2587,7 +1971,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="48" spans="4:5">
+    <row r="48" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D48" s="1" t="s">
         <v>89</v>
       </c>
@@ -2595,7 +1979,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="49" spans="4:5">
+    <row r="49" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D49" s="1" t="s">
         <v>91</v>
       </c>
@@ -2603,7 +1987,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="50" spans="4:5">
+    <row r="50" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D50" s="1" t="s">
         <v>93</v>
       </c>
@@ -2611,7 +1995,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="51" spans="4:5">
+    <row r="51" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D51" s="1" t="s">
         <v>95</v>
       </c>
@@ -2619,7 +2003,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="52" spans="4:5">
+    <row r="52" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D52" s="1" t="s">
         <v>97</v>
       </c>
@@ -2627,7 +2011,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="53" spans="4:5">
+    <row r="53" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D53" s="1" t="s">
         <v>99</v>
       </c>
@@ -2635,7 +2019,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="54" spans="4:5">
+    <row r="54" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D54" s="1" t="s">
         <v>101</v>
       </c>
@@ -2643,7 +2027,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="55" spans="4:5">
+    <row r="55" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D55" s="1" t="s">
         <v>103</v>
       </c>
@@ -2651,7 +2035,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="56" spans="4:5">
+    <row r="56" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D56" s="1" t="s">
         <v>105</v>
       </c>
@@ -2659,7 +2043,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="57" spans="4:5">
+    <row r="57" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D57" s="1" t="s">
         <v>107</v>
       </c>
@@ -2667,7 +2051,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="58" spans="4:5">
+    <row r="58" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D58" s="1" t="s">
         <v>109</v>
       </c>
@@ -2675,7 +2059,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="59" spans="4:5">
+    <row r="59" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D59" s="1" t="s">
         <v>111</v>
       </c>
@@ -2683,7 +2067,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="60" spans="4:5">
+    <row r="60" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D60" s="1" t="s">
         <v>113</v>
       </c>
@@ -2691,7 +2075,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="61" spans="4:5">
+    <row r="61" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D61" s="1" t="s">
         <v>115</v>
       </c>
@@ -2699,7 +2083,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="62" spans="4:5">
+    <row r="62" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D62" s="1" t="s">
         <v>117</v>
       </c>
@@ -2707,7 +2091,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="63" spans="4:5">
+    <row r="63" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D63" s="1" t="s">
         <v>119</v>
       </c>
@@ -2715,7 +2099,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="64" spans="4:5">
+    <row r="64" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D64" s="1" t="s">
         <v>121</v>
       </c>
@@ -2723,7 +2107,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="65" spans="4:5">
+    <row r="65" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D65" s="1" t="s">
         <v>123</v>
       </c>
@@ -2731,7 +2115,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="66" spans="4:5">
+    <row r="66" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D66" s="1" t="s">
         <v>125</v>
       </c>
@@ -2739,7 +2123,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="67" spans="4:5">
+    <row r="67" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D67" s="1" t="s">
         <v>127</v>
       </c>
@@ -2747,7 +2131,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="68" spans="4:5">
+    <row r="68" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D68" s="1" t="s">
         <v>129</v>
       </c>
@@ -2755,7 +2139,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="69" spans="4:5">
+    <row r="69" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D69" s="1" t="s">
         <v>131</v>
       </c>
@@ -2763,7 +2147,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="70" spans="4:5">
+    <row r="70" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D70" s="1" t="s">
         <v>133</v>
       </c>
@@ -2771,7 +2155,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="71" spans="4:5">
+    <row r="71" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D71" s="1" t="s">
         <v>135</v>
       </c>
@@ -2779,7 +2163,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="72" spans="4:5">
+    <row r="72" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D72" s="1" t="s">
         <v>137</v>
       </c>
@@ -2787,7 +2171,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="73" spans="4:7">
+    <row r="73" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D73" s="1" t="s">
         <v>139</v>
       </c>
@@ -2795,7 +2179,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="74" spans="4:7">
+    <row r="74" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D74" s="1" t="s">
         <v>141</v>
       </c>
@@ -2806,7 +2190,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="75" spans="4:7">
+    <row r="75" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D75" s="1" t="s">
         <v>144</v>
       </c>
@@ -2817,7 +2201,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="76" spans="4:7">
+    <row r="76" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D76" s="1" t="s">
         <v>147</v>
       </c>
@@ -2828,7 +2212,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="77" spans="4:7">
+    <row r="77" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D77" s="1" t="s">
         <v>150</v>
       </c>
@@ -2839,7 +2223,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="78" spans="4:7">
+    <row r="78" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D78" s="1" t="s">
         <v>153</v>
       </c>
@@ -2850,7 +2234,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="79" spans="4:7">
+    <row r="79" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D79" s="1" t="s">
         <v>156</v>
       </c>
@@ -2861,7 +2245,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="80" spans="4:7">
+    <row r="80" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D80" s="1" t="s">
         <v>159</v>
       </c>
@@ -2872,7 +2256,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="81" spans="4:7">
+    <row r="81" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D81" s="1" t="s">
         <v>162</v>
       </c>
@@ -2883,7 +2267,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="82" spans="4:7">
+    <row r="82" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D82" s="1" t="s">
         <v>165</v>
       </c>
@@ -2894,7 +2278,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="83" spans="4:7">
+    <row r="83" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D83" s="1" t="s">
         <v>168</v>
       </c>
@@ -2905,7 +2289,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="84" spans="4:7">
+    <row r="84" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D84" s="1" t="s">
         <v>170</v>
       </c>
@@ -2916,7 +2300,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="85" spans="4:7">
+    <row r="85" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D85" s="1" t="s">
         <v>172</v>
       </c>
@@ -2927,7 +2311,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="86" spans="4:7">
+    <row r="86" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D86" s="1" t="s">
         <v>174</v>
       </c>
@@ -2938,7 +2322,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="87" spans="4:7">
+    <row r="87" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D87" s="1" t="s">
         <v>176</v>
       </c>
@@ -2949,7 +2333,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="88" spans="4:7">
+    <row r="88" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D88" s="1" t="s">
         <v>178</v>
       </c>
@@ -2960,7 +2344,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="89" spans="4:7">
+    <row r="89" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D89" s="1" t="s">
         <v>180</v>
       </c>
@@ -2971,7 +2355,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="90" spans="4:7">
+    <row r="90" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D90" s="1" t="s">
         <v>182</v>
       </c>
@@ -2982,12 +2366,12 @@
         <v>167</v>
       </c>
     </row>
-    <row r="91" spans="7:7">
+    <row r="91" spans="4:7" x14ac:dyDescent="0.15">
       <c r="G91" s="1" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="92" spans="5:7">
+    <row r="92" spans="4:7" x14ac:dyDescent="0.15">
       <c r="E92" s="1" t="s">
         <v>185</v>
       </c>
@@ -2995,7 +2379,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="93" spans="5:7">
+    <row r="93" spans="4:7" x14ac:dyDescent="0.15">
       <c r="E93" s="1" t="s">
         <v>187</v>
       </c>
@@ -3003,7 +2387,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="94" spans="5:7">
+    <row r="94" spans="4:7" x14ac:dyDescent="0.15">
       <c r="E94" s="1" t="s">
         <v>188</v>
       </c>
@@ -3011,7 +2395,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="95" spans="5:7">
+    <row r="95" spans="4:7" x14ac:dyDescent="0.15">
       <c r="E95" s="1" t="s">
         <v>189</v>
       </c>
@@ -3019,7 +2403,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="96" spans="5:7">
+    <row r="96" spans="4:7" x14ac:dyDescent="0.15">
       <c r="E96" s="1" t="s">
         <v>120</v>
       </c>
@@ -3027,7 +2411,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="97" spans="5:7">
+    <row r="97" spans="4:7" x14ac:dyDescent="0.15">
       <c r="E97" s="1" t="s">
         <v>190</v>
       </c>
@@ -3035,7 +2419,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="98" spans="5:7">
+    <row r="98" spans="4:7" x14ac:dyDescent="0.15">
       <c r="E98" s="1" t="s">
         <v>191</v>
       </c>
@@ -3043,7 +2427,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="99" spans="5:7">
+    <row r="99" spans="4:7" x14ac:dyDescent="0.15">
       <c r="E99" s="1" t="s">
         <v>192</v>
       </c>
@@ -3051,7 +2435,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="100" spans="5:7">
+    <row r="100" spans="4:7" x14ac:dyDescent="0.15">
       <c r="E100" s="1" t="s">
         <v>193</v>
       </c>
@@ -3059,7 +2443,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="101" spans="4:7">
+    <row r="101" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D101" s="1" t="s">
         <v>194</v>
       </c>
@@ -3070,7 +2454,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="102" spans="4:7">
+    <row r="102" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D102" s="1" t="s">
         <v>197</v>
       </c>
@@ -3081,7 +2465,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="103" spans="4:7">
+    <row r="103" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D103" s="1" t="s">
         <v>199</v>
       </c>
@@ -3092,7 +2476,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="104" spans="4:7">
+    <row r="104" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D104" s="1" t="s">
         <v>201</v>
       </c>
@@ -3103,7 +2487,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="105" spans="4:7">
+    <row r="105" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D105" s="1" t="s">
         <v>203</v>
       </c>
@@ -3114,7 +2498,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="106" spans="4:7">
+    <row r="106" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D106" s="1" t="s">
         <v>204</v>
       </c>
@@ -3125,7 +2509,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="107" spans="4:7">
+    <row r="107" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D107" s="1" t="s">
         <v>206</v>
       </c>
@@ -3136,7 +2520,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="108" spans="4:7">
+    <row r="108" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D108" s="1" t="s">
         <v>208</v>
       </c>
@@ -3147,7 +2531,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="109" spans="4:7">
+    <row r="109" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D109" s="1" t="s">
         <v>210</v>
       </c>
@@ -3158,7 +2542,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="110" spans="4:7">
+    <row r="110" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D110" s="1" t="s">
         <v>212</v>
       </c>
@@ -3169,7 +2553,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="111" spans="4:7">
+    <row r="111" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D111" s="1" t="s">
         <v>215</v>
       </c>
@@ -3180,7 +2564,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="112" spans="4:7">
+    <row r="112" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D112" s="1" t="s">
         <v>218</v>
       </c>
@@ -3191,7 +2575,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="113" spans="4:7">
+    <row r="113" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D113" s="1" t="s">
         <v>221</v>
       </c>
@@ -3202,7 +2586,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="114" spans="4:7">
+    <row r="114" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D114" s="1" t="s">
         <v>224</v>
       </c>
@@ -3213,102 +2597,102 @@
         <v>226</v>
       </c>
     </row>
-    <row r="115" spans="7:7">
+    <row r="115" spans="4:7" x14ac:dyDescent="0.15">
       <c r="G115" s="1" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="116" spans="7:7">
+    <row r="116" spans="4:7" x14ac:dyDescent="0.15">
       <c r="G116" s="1" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="117" spans="7:7">
+    <row r="117" spans="4:7" x14ac:dyDescent="0.15">
       <c r="G117" s="1" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="118" spans="7:7">
+    <row r="118" spans="4:7" x14ac:dyDescent="0.15">
       <c r="G118" s="1" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="119" spans="7:7">
+    <row r="119" spans="4:7" x14ac:dyDescent="0.15">
       <c r="G119" s="1" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="120" spans="7:7">
+    <row r="120" spans="4:7" x14ac:dyDescent="0.15">
       <c r="G120" s="1" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="121" spans="7:7">
+    <row r="121" spans="4:7" x14ac:dyDescent="0.15">
       <c r="G121" s="1" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="122" spans="7:7">
+    <row r="122" spans="4:7" x14ac:dyDescent="0.15">
       <c r="G122" s="1" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="123" spans="7:7">
+    <row r="123" spans="4:7" x14ac:dyDescent="0.15">
       <c r="G123" s="1" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="124" spans="7:7">
+    <row r="124" spans="4:7" x14ac:dyDescent="0.15">
       <c r="G124" s="1" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="125" spans="7:7">
+    <row r="125" spans="4:7" x14ac:dyDescent="0.15">
       <c r="G125" s="1" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="126" spans="7:7">
+    <row r="126" spans="4:7" x14ac:dyDescent="0.15">
       <c r="G126" s="1" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="127" spans="7:7">
+    <row r="127" spans="4:7" x14ac:dyDescent="0.15">
       <c r="G127" s="1" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="128" spans="7:7">
+    <row r="128" spans="4:7" x14ac:dyDescent="0.15">
       <c r="G128" s="1" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="129" spans="7:7">
+    <row r="129" spans="4:7" x14ac:dyDescent="0.15">
       <c r="G129" s="1" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="130" spans="7:7">
+    <row r="130" spans="4:7" x14ac:dyDescent="0.15">
       <c r="G130" s="1" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="131" spans="7:7">
+    <row r="131" spans="4:7" x14ac:dyDescent="0.15">
       <c r="G131" s="1" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="132" spans="7:7">
+    <row r="132" spans="4:7" x14ac:dyDescent="0.15">
       <c r="G132" s="1" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="133" spans="7:7">
+    <row r="133" spans="4:7" x14ac:dyDescent="0.15">
       <c r="G133" s="1" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="134" spans="4:7">
+    <row r="134" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D134" s="1" t="s">
         <v>242</v>
       </c>
@@ -3316,7 +2700,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="135" spans="4:5">
+    <row r="135" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D135" s="1" t="s">
         <v>244</v>
       </c>
@@ -3324,7 +2708,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="136" spans="4:5">
+    <row r="136" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D136" s="1" t="s">
         <v>246</v>
       </c>
@@ -3332,7 +2716,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="137" spans="4:5">
+    <row r="137" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D137" s="1" t="s">
         <v>248</v>
       </c>
@@ -3340,7 +2724,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="138" spans="4:5">
+    <row r="138" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D138" s="1" t="s">
         <v>250</v>
       </c>
@@ -3348,7 +2732,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="139" spans="4:5">
+    <row r="139" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D139" s="1" t="s">
         <v>252</v>
       </c>
@@ -3356,7 +2740,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="140" spans="4:7">
+    <row r="140" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D140" s="1" t="s">
         <v>254</v>
       </c>
@@ -3364,7 +2748,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="141" spans="4:7">
+    <row r="141" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D141" s="1" t="s">
         <v>256</v>
       </c>
@@ -3375,7 +2759,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="142" spans="4:7">
+    <row r="142" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D142" s="1" t="s">
         <v>258</v>
       </c>
@@ -3386,7 +2770,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="143" spans="4:7">
+    <row r="143" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D143" s="1" t="s">
         <v>260</v>
       </c>
@@ -3397,7 +2781,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="144" spans="4:7">
+    <row r="144" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D144" s="1" t="s">
         <v>262</v>
       </c>
@@ -3408,7 +2792,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="145" spans="4:7">
+    <row r="145" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D145" s="1" t="s">
         <v>264</v>
       </c>
@@ -3419,7 +2803,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="146" spans="4:7">
+    <row r="146" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D146" s="1" t="s">
         <v>266</v>
       </c>
@@ -3430,7 +2814,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="147" spans="4:7">
+    <row r="147" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D147" s="1" t="s">
         <v>268</v>
       </c>
@@ -3441,7 +2825,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="148" spans="4:7">
+    <row r="148" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D148" s="1" t="s">
         <v>270</v>
       </c>
@@ -3452,7 +2836,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="149" spans="4:7">
+    <row r="149" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D149" s="1" t="s">
         <v>272</v>
       </c>
@@ -3460,7 +2844,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="150" spans="4:7">
+    <row r="150" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D150" s="1" t="s">
         <v>274</v>
       </c>
@@ -3468,7 +2852,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="151" spans="4:7">
+    <row r="151" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D151" s="1" t="s">
         <v>276</v>
       </c>
@@ -3476,7 +2860,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="152" spans="4:7">
+    <row r="152" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D152" s="1" t="s">
         <v>278</v>
       </c>
@@ -3484,7 +2868,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="153" spans="4:7">
+    <row r="153" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D153" s="1" t="s">
         <v>280</v>
       </c>
@@ -3492,7 +2876,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="154" spans="4:7">
+    <row r="154" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D154" s="1" t="s">
         <v>282</v>
       </c>
@@ -3500,7 +2884,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="155" spans="4:7">
+    <row r="155" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D155" s="1" t="s">
         <v>284</v>
       </c>
@@ -3508,7 +2892,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="156" spans="4:7">
+    <row r="156" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D156" s="1" t="s">
         <v>286</v>
       </c>
@@ -3516,7 +2900,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="157" spans="4:7">
+    <row r="157" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D157" s="1" t="s">
         <v>288</v>
       </c>
@@ -3524,32 +2908,32 @@
         <v>289</v>
       </c>
     </row>
-    <row r="158" spans="5:5">
+    <row r="158" spans="4:7" x14ac:dyDescent="0.15">
       <c r="E158" s="1" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="159" spans="5:5">
+    <row r="159" spans="4:7" x14ac:dyDescent="0.15">
       <c r="E159" s="1" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="160" spans="5:5">
+    <row r="160" spans="4:7" x14ac:dyDescent="0.15">
       <c r="E160" s="1" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="161" spans="5:5">
+    <row r="161" spans="5:7" x14ac:dyDescent="0.15">
       <c r="E161" s="1" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="162" spans="5:5">
+    <row r="162" spans="5:7" x14ac:dyDescent="0.15">
       <c r="E162" s="1" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="163" spans="5:7">
+    <row r="163" spans="5:7" x14ac:dyDescent="0.15">
       <c r="E163" s="1" t="s">
         <v>295</v>
       </c>
@@ -3557,7 +2941,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="164" spans="5:7">
+    <row r="164" spans="5:7" x14ac:dyDescent="0.15">
       <c r="E164" s="1" t="s">
         <v>297</v>
       </c>
@@ -3565,7 +2949,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="165" spans="5:7">
+    <row r="165" spans="5:7" x14ac:dyDescent="0.15">
       <c r="E165" s="1" t="s">
         <v>298</v>
       </c>
@@ -3573,7 +2957,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="166" spans="5:7">
+    <row r="166" spans="5:7" x14ac:dyDescent="0.15">
       <c r="E166" s="1" t="s">
         <v>299</v>
       </c>
@@ -3581,7 +2965,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="167" spans="5:7">
+    <row r="167" spans="5:7" x14ac:dyDescent="0.15">
       <c r="E167" s="1" t="s">
         <v>90</v>
       </c>
@@ -3589,7 +2973,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="168" spans="5:7">
+    <row r="168" spans="5:7" x14ac:dyDescent="0.15">
       <c r="E168" s="1" t="s">
         <v>300</v>
       </c>
@@ -3597,7 +2981,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="169" spans="5:7">
+    <row r="169" spans="5:7" x14ac:dyDescent="0.15">
       <c r="E169" s="1" t="s">
         <v>301</v>
       </c>
@@ -3605,7 +2989,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="170" spans="5:7">
+    <row r="170" spans="5:7" x14ac:dyDescent="0.15">
       <c r="E170" s="1" t="s">
         <v>302</v>
       </c>
@@ -3613,7 +2997,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="171" spans="5:7">
+    <row r="171" spans="5:7" x14ac:dyDescent="0.15">
       <c r="E171" s="1" t="s">
         <v>303</v>
       </c>
@@ -3621,57 +3005,57 @@
         <v>296</v>
       </c>
     </row>
-    <row r="172" spans="7:7">
+    <row r="172" spans="5:7" x14ac:dyDescent="0.15">
       <c r="G172" s="1" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="173" spans="7:7">
+    <row r="173" spans="5:7" x14ac:dyDescent="0.15">
       <c r="G173" s="1" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="174" spans="7:7">
+    <row r="174" spans="5:7" x14ac:dyDescent="0.15">
       <c r="G174" s="1" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="175" spans="7:7">
+    <row r="175" spans="5:7" x14ac:dyDescent="0.15">
       <c r="G175" s="1" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="176" spans="7:7">
+    <row r="176" spans="5:7" x14ac:dyDescent="0.15">
       <c r="G176" s="1" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="177" spans="7:7">
+    <row r="177" spans="5:7" x14ac:dyDescent="0.15">
       <c r="G177" s="1" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="178" spans="7:7">
+    <row r="178" spans="5:7" x14ac:dyDescent="0.15">
       <c r="G178" s="1" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="179" spans="7:7">
+    <row r="179" spans="5:7" x14ac:dyDescent="0.15">
       <c r="G179" s="1" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="180" spans="7:7">
+    <row r="180" spans="5:7" x14ac:dyDescent="0.15">
       <c r="G180" s="1" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="181" spans="7:7">
+    <row r="181" spans="5:7" x14ac:dyDescent="0.15">
       <c r="G181" s="1" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="182" spans="5:7">
+    <row r="182" spans="5:7" x14ac:dyDescent="0.15">
       <c r="E182" s="1" t="s">
         <v>306</v>
       </c>
@@ -3679,7 +3063,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="183" spans="5:7">
+    <row r="183" spans="5:7" x14ac:dyDescent="0.15">
       <c r="E183" s="1" t="s">
         <v>307</v>
       </c>
@@ -3687,7 +3071,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="184" spans="5:7">
+    <row r="184" spans="5:7" x14ac:dyDescent="0.15">
       <c r="E184" s="1" t="s">
         <v>308</v>
       </c>
@@ -3695,7 +3079,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="185" spans="5:7">
+    <row r="185" spans="5:7" x14ac:dyDescent="0.15">
       <c r="E185" s="1" t="s">
         <v>309</v>
       </c>
@@ -3703,7 +3087,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="186" spans="5:7">
+    <row r="186" spans="5:7" x14ac:dyDescent="0.15">
       <c r="E186" s="1" t="s">
         <v>310</v>
       </c>
@@ -3711,7 +3095,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="187" spans="5:7">
+    <row r="187" spans="5:7" x14ac:dyDescent="0.15">
       <c r="E187" s="1" t="s">
         <v>311</v>
       </c>
@@ -3719,7 +3103,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="188" spans="5:7">
+    <row r="188" spans="5:7" x14ac:dyDescent="0.15">
       <c r="E188" s="1" t="s">
         <v>312</v>
       </c>
@@ -3727,7 +3111,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="189" spans="5:7">
+    <row r="189" spans="5:7" x14ac:dyDescent="0.15">
       <c r="E189" s="1" t="s">
         <v>313</v>
       </c>
@@ -3735,52 +3119,52 @@
         <v>305</v>
       </c>
     </row>
-    <row r="190" spans="7:7">
+    <row r="190" spans="5:7" x14ac:dyDescent="0.15">
       <c r="G190" s="1" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="191" spans="7:7">
+    <row r="191" spans="5:7" x14ac:dyDescent="0.15">
       <c r="G191" s="1" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="192" spans="7:7">
+    <row r="192" spans="5:7" x14ac:dyDescent="0.15">
       <c r="G192" s="1" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="193" spans="7:7">
+    <row r="193" spans="4:7" x14ac:dyDescent="0.15">
       <c r="G193" s="1" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="194" spans="7:7">
+    <row r="194" spans="4:7" x14ac:dyDescent="0.15">
       <c r="G194" s="1" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="195" spans="7:7">
+    <row r="195" spans="4:7" x14ac:dyDescent="0.15">
       <c r="G195" s="1" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="196" spans="7:7">
+    <row r="196" spans="4:7" x14ac:dyDescent="0.15">
       <c r="G196" s="1" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="197" spans="7:7">
+    <row r="197" spans="4:7" x14ac:dyDescent="0.15">
       <c r="G197" s="1" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="198" spans="7:7">
+    <row r="198" spans="4:7" x14ac:dyDescent="0.15">
       <c r="G198" s="1" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="199" spans="4:7">
+    <row r="199" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D199" s="1" t="s">
         <v>323</v>
       </c>
@@ -3788,7 +3172,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="200" spans="4:7">
+    <row r="200" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D200" s="1" t="s">
         <v>325</v>
       </c>
@@ -3796,7 +3180,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="201" spans="4:7">
+    <row r="201" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D201" s="1" t="s">
         <v>327</v>
       </c>
@@ -3804,7 +3188,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="202" spans="4:7">
+    <row r="202" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D202" s="1" t="s">
         <v>329</v>
       </c>
@@ -3812,7 +3196,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="203" spans="4:7">
+    <row r="203" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D203" s="1" t="s">
         <v>331</v>
       </c>
@@ -3820,7 +3204,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="204" spans="4:7">
+    <row r="204" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D204" s="1" t="s">
         <v>333</v>
       </c>
@@ -3828,7 +3212,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="205" spans="4:7">
+    <row r="205" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D205" s="1" t="s">
         <v>335</v>
       </c>
@@ -3836,7 +3220,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="206" spans="4:7">
+    <row r="206" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D206" s="1" t="s">
         <v>337</v>
       </c>
@@ -3844,7 +3228,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="207" spans="4:7">
+    <row r="207" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D207" s="1" t="s">
         <v>339</v>
       </c>
@@ -3852,7 +3236,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="208" spans="4:7">
+    <row r="208" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D208" s="1" t="s">
         <v>341</v>
       </c>
@@ -3860,12 +3244,12 @@
         <v>342</v>
       </c>
     </row>
-    <row r="209" spans="7:7">
+    <row r="209" spans="4:7" x14ac:dyDescent="0.15">
       <c r="G209" s="1" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="210" spans="5:7">
+    <row r="210" spans="4:7" x14ac:dyDescent="0.15">
       <c r="E210" s="1" t="s">
         <v>306</v>
       </c>
@@ -3873,7 +3257,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="211" spans="5:7">
+    <row r="211" spans="4:7" x14ac:dyDescent="0.15">
       <c r="E211" s="1" t="s">
         <v>307</v>
       </c>
@@ -3881,7 +3265,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="212" spans="5:7">
+    <row r="212" spans="4:7" x14ac:dyDescent="0.15">
       <c r="E212" s="1" t="s">
         <v>308</v>
       </c>
@@ -3889,7 +3273,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="213" spans="5:7">
+    <row r="213" spans="4:7" x14ac:dyDescent="0.15">
       <c r="E213" s="1" t="s">
         <v>309</v>
       </c>
@@ -3897,7 +3281,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="214" spans="5:7">
+    <row r="214" spans="4:7" x14ac:dyDescent="0.15">
       <c r="E214" s="1" t="s">
         <v>310</v>
       </c>
@@ -3905,7 +3289,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="215" spans="5:7">
+    <row r="215" spans="4:7" x14ac:dyDescent="0.15">
       <c r="E215" s="1" t="s">
         <v>311</v>
       </c>
@@ -3913,7 +3297,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="216" spans="5:7">
+    <row r="216" spans="4:7" x14ac:dyDescent="0.15">
       <c r="E216" s="1" t="s">
         <v>312</v>
       </c>
@@ -3921,7 +3305,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="217" spans="5:7">
+    <row r="217" spans="4:7" x14ac:dyDescent="0.15">
       <c r="E217" s="1" t="s">
         <v>313</v>
       </c>
@@ -3929,7 +3313,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="218" spans="4:7">
+    <row r="218" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D218" s="1" t="s">
         <v>344</v>
       </c>
@@ -3937,7 +3321,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="219" spans="4:7">
+    <row r="219" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D219" s="1" t="s">
         <v>346</v>
       </c>
@@ -3948,7 +3332,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="220" spans="4:7">
+    <row r="220" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D220" s="1" t="s">
         <v>347</v>
       </c>
@@ -3959,7 +3343,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="221" spans="4:7">
+    <row r="221" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D221" s="1" t="s">
         <v>348</v>
       </c>
@@ -3970,7 +3354,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="222" spans="4:7">
+    <row r="222" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D222" s="1" t="s">
         <v>349</v>
       </c>
@@ -3981,7 +3365,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="223" spans="4:7">
+    <row r="223" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D223" s="1" t="s">
         <v>350</v>
       </c>
@@ -3992,7 +3376,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="224" spans="4:7">
+    <row r="224" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D224" s="1" t="s">
         <v>351</v>
       </c>
@@ -4003,7 +3387,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="225" spans="4:7">
+    <row r="225" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D225" s="1" t="s">
         <v>352</v>
       </c>
@@ -4014,7 +3398,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="226" spans="4:7">
+    <row r="226" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D226" s="1" t="s">
         <v>353</v>
       </c>
@@ -4025,7 +3409,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="227" spans="4:7">
+    <row r="227" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D227" s="1" t="s">
         <v>354</v>
       </c>
@@ -4036,7 +3420,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="228" spans="4:7">
+    <row r="228" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D228" s="1" t="s">
         <v>357</v>
       </c>
@@ -4047,7 +3431,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="229" spans="4:7">
+    <row r="229" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D229" s="1" t="s">
         <v>359</v>
       </c>
@@ -4058,7 +3442,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="230" spans="4:7">
+    <row r="230" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D230" s="1" t="s">
         <v>361</v>
       </c>
@@ -4069,7 +3453,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="231" spans="4:7">
+    <row r="231" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D231" s="1" t="s">
         <v>363</v>
       </c>
@@ -4080,7 +3464,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="232" spans="4:7">
+    <row r="232" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D232" s="1" t="s">
         <v>364</v>
       </c>
@@ -4091,7 +3475,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="233" spans="4:7">
+    <row r="233" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D233" s="1" t="s">
         <v>366</v>
       </c>
@@ -4102,7 +3486,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="234" spans="4:7">
+    <row r="234" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D234" s="1" t="s">
         <v>368</v>
       </c>
@@ -4113,7 +3497,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="235" spans="4:7">
+    <row r="235" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D235" s="1" t="s">
         <v>370</v>
       </c>
@@ -4124,7 +3508,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="236" spans="5:7">
+    <row r="236" spans="4:7" x14ac:dyDescent="0.15">
       <c r="E236" s="1" t="s">
         <v>295</v>
       </c>
@@ -4132,7 +3516,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="237" spans="5:7">
+    <row r="237" spans="4:7" x14ac:dyDescent="0.15">
       <c r="E237" s="1" t="s">
         <v>297</v>
       </c>
@@ -4140,7 +3524,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="238" spans="5:7">
+    <row r="238" spans="4:7" x14ac:dyDescent="0.15">
       <c r="E238" s="1" t="s">
         <v>298</v>
       </c>
@@ -4148,7 +3532,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="239" spans="5:7">
+    <row r="239" spans="4:7" x14ac:dyDescent="0.15">
       <c r="E239" s="1" t="s">
         <v>299</v>
       </c>
@@ -4156,7 +3540,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="240" spans="5:7">
+    <row r="240" spans="4:7" x14ac:dyDescent="0.15">
       <c r="E240" s="1" t="s">
         <v>90</v>
       </c>
@@ -4164,7 +3548,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="241" spans="5:7">
+    <row r="241" spans="4:7" x14ac:dyDescent="0.15">
       <c r="E241" s="1" t="s">
         <v>300</v>
       </c>
@@ -4172,7 +3556,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="242" spans="5:7">
+    <row r="242" spans="4:7" x14ac:dyDescent="0.15">
       <c r="E242" s="1" t="s">
         <v>301</v>
       </c>
@@ -4180,7 +3564,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="243" spans="5:7">
+    <row r="243" spans="4:7" x14ac:dyDescent="0.15">
       <c r="E243" s="1" t="s">
         <v>302</v>
       </c>
@@ -4188,7 +3572,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="244" spans="5:7">
+    <row r="244" spans="4:7" x14ac:dyDescent="0.15">
       <c r="E244" s="1" t="s">
         <v>303</v>
       </c>
@@ -4196,7 +3580,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="245" spans="4:7">
+    <row r="245" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D245" s="1" t="s">
         <v>373</v>
       </c>
@@ -4204,7 +3588,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="246" spans="4:7">
+    <row r="246" spans="4:7" x14ac:dyDescent="0.15">
       <c r="D246" s="1" t="s">
         <v>375</v>
       </c>
@@ -4213,32 +3597,30 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="300"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="300"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="300"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/Luban/Excel/宝器.xlsx
+++ b/Luban/Excel/宝器.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDB4A1E9-3936-4D0F-AACA-7C4B9AF8E295}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="宝器" sheetId="1" r:id="rId1"/>
@@ -1184,6 +1184,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1191,6 +1192,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
